--- a/output_excel/17064027.xlsx
+++ b/output_excel/17064027.xlsx
@@ -32,11 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C6500"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="5">
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -563,19 +563,27 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>BM | P2 | 201734 | AVENIDA | P1-11 | 175ET005296879 | 7275 | BF-A | 15KV_1L(C) | GUINLE | 15KV_1F1(A) | FERRAGEM | CE1 | PRE1 | 1x2x4AC | CAMINHÃO | (DCIM) | BF-A | 1AF(1) | V1-9 | 25KVA | (DCIM) | 1AF(1) | 112,5KVA | 1x2x4AC | CE1 | 112,5KVA</t>
+          <t>BM | GUINLE | 7275 | AVENIDA | CE1 | BF-A | PRE1 | 201734 | 15KV_1L(C) | CABOS | C10X300112,5KVAB1M112,5KVASMTG | 175ET005296879 | 15KV_1F1(A)</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>CRITICO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -608,20 +616,20 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>BM | P2 | GUINLE | AVENIDA | 7275 | BF-A | 201734 | 15KV_1L(C) | CE1 | P31 | PRE1 | 175ET005296879 | 15KV_1F1(A) | CABOS</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+          <t>BM | GUINLE | AVENIDA</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NAO</t>
         </is>
       </c>
     </row>
@@ -657,13 +665,13 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>P31 | CABOS | C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | PRE1 | P4-30 | CE2 | CONEX. | P5 | GUINLE | P2 | 4957 | CE4</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
+          <t>CABOS | C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | PRE1 | CE2</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -694,27 +702,19 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>P31 | CABOS | P4-30 | C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | PRE1 | 4957 | CE2 | P2 | CONEX. | EP | CE1 | GUIA | GUINLE | AVENIDA | PRE1 | P5 | BM | C10X300112,5KVAB1M112,5KVASMTG | FERRAGEM | EXPOSTA | PERTO | AVENIDA</t>
+          <t>GUIA | AVENIDA | 4957 | FERRAGEM | AVENIDA | EP | PERTO | PRUMO | EXPOSTA | CLANDESTINOS: | Q/R</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -755,13 +755,13 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>C12X600112,5KVAB2M | PRE1 | CE2 | CE2 | PRE1 | C12X600112,5KVAB2M | Q/R | ESTR. | P7x | EXPOSTA | P8 | CE4 | FERRAGEM | AVENIDA | GUIA | PRE4 | P6 | AVENIDA | C12X600112,5KVAB4M</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
+          <t>C12X600112,5KVAB2M | PRE1 | CE2 | CE2 | PRE1 | C12X600112,5KVAB2M | Q/R | ESTR.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -804,13 +804,13 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>PODA | P7x | P6 | C12X1000112,5KVAB4F112,5KVAS44(1) | PRE4 | CE4 | P8 | P5 | ESTR. | CONEX.</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
+          <t>PRE4 | C12X1000112,5KVAB4F112,5KVAS44(1) | CE4 | PODA</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -853,13 +853,13 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>P7x | P8 | ESTR. | P6 | PODA | CE2 | PRE1 | C12X600112,5KVAB2M | CE2 | Q/R | PRE1 | C12X600112,5KVAB2M | EXPOSTA | P5 | C12X1000112,5KVAB4F112,5KVAS44(1) | CONEX. | P9</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
+          <t>CE2 | PRE1 | C12X600112,5KVAB2M | CE4 | PRE4 | C12X600112,5KVAB2M | C12X600112,5KVAB4M | PRE1 | PODA | EP | CE2 | PODAS | ESTR.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -898,13 +898,13 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>V1-2 | 35.5M | 3x185AX(5AZN) | COMPARTILHANTES | 1x3x240(120)AX | LEGENDA | 30K | 112,5KVA | MT | COMPARTILHANTES | 3x336AN(3/0AN) | 3x185AX(5AZN) | 3x336AN(3/0AN) | 1x3x240(120)AX | 1X2X4AC | CALÇADA | MT | V2-3 | 0099 | CMB | BT | POSTES | LADO | 112,5KVA | 112,5KVA | DOS | TRECHO | 34.5M | 3x185AX(5AZN) | 30K | NVL | 17064027 | BF-A | V5-6 | 3x336AN | TODO | 1x3x240(120)AX | 12.3M</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
+          <t>35.5M | 3x185AX(5AZN) | COMPARTILHANTES | 1x3x240(120)AX | LEGENDA | 3 | 1 | MT | COMPARTILHANTES</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -943,13 +943,13 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12.3M | V5-6 | V6-7 | VÃOS | DOS | 112,5KVA | 3x336AN(3/0AN) | 3x185AX(5AZN) | 1x3x240(120)AX | MT | 3x185AX(5AZN) | 1x3x240(120)AX | 17.3M | MT | 112,5KVA | 112,5KVA | 3x336AN(3/0AN) | LEGENDA | 112,5KVA | 3x185AX(5AZN) | 3x185AX(5AZN) | 1x3x240(120)AX | 1x3x240(120)AX | 3x336AN(3/0AN) | MT | MT</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
+          <t>12.3M | 3x336AN(3/0AN) | 17.3M | 2 | 1x3x240(120)AX | 1 | MT | 3x185AX(5AZN) | MT | VÃOS | 1x3x240(120)AX</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -988,13 +988,13 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>112,5KVA | V9-10 | 27.8M | 3x185AX(5AZN) | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | 1x3x240(120)AX | 3x336AN(3/0AN) | MT | C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL | FORA | V10-11 | 112,5KVA | CLANDESTINOS: | INSTALAR | PRUMO | 18.8M | 3x185AX(5AZN) | PERTO | 12.3M | V5-6 | 1x3x240(120)AX | VÃOS | AVENIDA | FERRAGEM | EP | 3x336AN(3/0AN) | AVENIDA</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
+          <t>2 | 27.8M | 3x185AX(5AZN) | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | 1x3x240(120)AX | 3x336AN(3/0AN) | MT | C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL | FORA</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1037,13 +1037,13 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>P9 | P8 | EP | 15681 | CE4 | PODAS | PRE4 | 112,5KVA | C12X600112,5KVAB4M | P7x</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
+          <t>EP | 15681 | PODAS | 2 | CE4 | PRE4 | C12X600112,5KVAB4M</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -1075,20 +1075,20 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17.3m</t>
+          <t>16.3m</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3x336AN(3/0AN) | MT | 112,5KVA | 1x3x240(120)AX | 3x185AX(5AZN) | 3x185AX(5AZN) | 112,5KVA | 1x3x240(120)AX | V7-8 | 17.3M | 16.3M | 3x336AN(3/0AN) | MT | V6-7 | 34.5M | 3x336AN(3/0AN) | MT | V2-3 | 112,5KVA | 1x3x240(120)AX | 3M | V8-9 | 3x185AX(5AZN) | 3x185AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
+          <t>3x336AN(3/0AN) | 16.3M | 2 | 17.3M | MT | 1x3x240(120)AX | 3x185AX(5AZN) | 3x185AX(5AZN) | 2 | 1x3x240(120)AX</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1127,20 +1127,20 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18.8M | V10-11 | 27.8M | 112,5KVA | 3x336AN(3/0AN) | V9-10 | V11-12 | 3x185AX(5AZN) | 3x336AN(3/0AN) | 1x3x240(120)AX | MT | 1x3x240(120)AX | MT | 13.2M | 3x185AX(5AZN) | 112,5KVA | 112,5KVA | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1)</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+          <t>18.8M | 27.8M</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NAO</t>
         </is>
       </c>
     </row>
@@ -1172,13 +1172,13 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3x336AN(3/0AN) | 1x3x240(120)AX | 1X2X4AC | 3x185AX(5AZN) | MT | 30K | 34.5M | BT | V2-3 | V3-4 | 1X2X4AC | BT | 3x185AX(5AZN) | 3M | 3x336AN(3/0AN) | MT | 1x3x240(120)AX | 1x3x240(120)AX | 3x336AN(3/0AN) | MT | MT | 1x3x240(120)AX | 3x185AX(5AZN) | 35.5M | 1X2X4AC | 3x185AX(5AZN) | BT | 3x185AX(5AZN) | 3x336AN(3/0AN) | 112,5KVA | 30K</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
+          <t>34.5M | 3x185AX(5AZN) | 1x3x240(120)AX | MT | 3 | 2 | MT | 3x336AN(3/0AN)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1213,13 +1213,13 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>P9 | EP | 15681 | P8 | PODAS | 112,5KVA | CABOS | P10 | CE4 | PRE4</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
+          <t>EP | 15681 | PODAS | 2 | CABOS | CE4 | PRE4</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1258,13 +1258,13 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>V7-8 | 16.3M | 17.3M | 3x185AX(5AZN) | MT | 112,5KVA | 112,5KVA | 1x3x240(120)AX | 3x336AN(3/0AN) | 1x3x240(120)AX | MT | V8-9 | 3x185AX(5AZN) | 3x336AN(3/0AN) | 3x336AN(3/0AN) | V6-7 | 1x3x240(120)AX | MT | 3x185AX(5AZN) | 3x336AN(3/0AN) | 1x3x240(120)AX | MT | 17.2M | 3x185AX(5AZN) | 112,5KVA | 112,5KVA | 112,5KVA | 30K | 3x185AX(5AZN) | V11-12 | 3x185AX(5AZN) | MT</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
+          <t>16.3M | 3x185AX(5AZN) | 1x3x240(120)AX | 1 | MT | 2 | 17.3M | MT</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1303,13 +1303,13 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>V11-12 | 13.2M | 18.8M | 112,5KVA | 3x336AN(3/0AN) | V12-13 | 3x185AX(5AZN) | 3x336AN(3/0AN) | V10-11 | 1x3x240(120)AX | MT | 1x3x240(120)AX | MT | 34.9M | 3x185AX(5AZN) | CE1 | 30K | 112,5KVA | CE1 | PRE1 | PRE1</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
+          <t>13.2M | 3x336AN(3/0AN) | 1 | 1x3x240(120)AX | 3x185AX(5AZN) | MT | 34.9M</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1341,20 +1341,20 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13.7m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1X2X4AC | 3x336AN(3/0AN) | BT | 112,5KVA | MT | 1x3x240(120)AX | 3x185AX(5AZN) | V4-5 | 3x185AX(5AZN) | 1x3x240(120)AX | 13.7M | V3-4 | 3x336AN(3/0AN) | 3M | MT | 1X2X4AC | BT | 1X2X4AC | BT | 3x336AN(3/0AN) | MT | 1x3x240(120)AX</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
+          <t>3M | 3x185AX(5AZN) | 1X2X4AC | 3x336AN(3/0AN) | 1x3x240(120)AX | 3x336AN(3/0AN) | BT | 1X2X4AC | MT | MT | BT | 1x3x240(120)AX</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1397,13 +1397,13 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>P10 | PODAS | 112,5KVA | P11 | EP | (DCIM) | 15681 | CABOS | B1F | C12X600112,5KVAB4M | BT | P9 | 3x336AN | PRE1 | CE1 | C12X600112,5KVAB4M | PRE4 | ANCORAR | P12 | (DCIM) | CE4</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="n">
+          <t>PODAS | 2 | (DCIM) | B1F | EP | BT | CABOS | 3x336AN | PRE1 | C12X600112,5KVAB4M | CE1 | C12X600112,5KVAB4M | 15681 | ANCORAR | (DCIM) | PRE4 | 13200 | 1RU6A | 563620 | BF-A | (DCIM) | CE4</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -1442,13 +1442,13 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>V8-9 | 17.2M | 16.3M | MT | 3x185AX(5AZN) | 112,5KVA | 30K | 3x336AN(3/0AN) | 1x3x240(120)AX | 1x3x240(120)AX | 3x336AN(3/0AN) | V7-8 | 3x185AX(5AZN) | 3x336AN(3/0AN) | MT | 3x185AX(5AZN) | 1x3x240(120)AX | MT | 1x3x240(120)AX | 3x336AN(3/0AN) | MT | 3x185AX(5AZN) | 112,5KVA | 112,5KVA | V12-13 | MT</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
+          <t>2 | 17.2M | 3x336AN(3/0AN) | 3x185AX(5AZN) | 1x3x240(120)AX | MT | 3x336AN(3/0AN) | 1x3x240(120)AX | MT | 16.3M | 3x185AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1487,13 +1487,13 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>V12-13 | 34.9M | CE1 | PRE1 | C10x600,B1M,M3F | 13.2M | 112,5KVA112,5KVA112,5KVA | C12X600112,5KVAB1F112,5KVAET4A | 30K | 3x336AN(3/0AN) | 3x336AN(3/0AN) | V11-12 | 3x185AX(5AZN) | 175ET005296879 | 1x3x240(120)AX | MT | 1x3x240(120)AX | MT | (DCIM) | 3x185AX(5AZN) | 563620 | 112,5KVA | 15KV_1F1(A) | C12X600112,5KVAB4M | PRE1</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
+          <t>34.9M | PRE1 | CE1 | C10x600,B1M,M3F | C12X600112,5KVAB1F112,5KVAET4A | 3x336AN(3/0AN) | 3 | 112112,5KVA112,5KVA | 1x3x240(120)AX | 3x185AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1532,13 +1532,13 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>V4-5 | 13.7M | 1X2X4AC | 3M | 112,5KVA | 3x185AX(5AZN) | 3x336AN(3/0AN) | 1x3x240(120)AX | MT | 3x336AN(3/0AN) | 3x185AX(5AZN) | BT | 1x3x240(120)AX | MT | 112,5KVA | 1X2X4AC | 3x336AN(3/0AN) | MT | 1x3x240(120)AX | MT | V3-4 | BT | 3x336AN(3/0AN) | 1x3x240(120)AX | 3x185AX(5AZN) | 3x185AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
+          <t>13.7M | 1X2X4AC | 3M | 1 | 3x185AX(5AZN) | 3x336AN(3/0AN) | 1x3x240(120)AX | MT</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1581,13 +1581,13 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>P11 | (DCIM) | B1F | P12 | BT | 3x336AN | ANCORAR | (DCIM) | BCU | (DCIM) | 13200 | P10 | BF-A | CABOS | ANCORAR | BT | 563620 | 3x336AN | 112,5KVA | 15KV_1F1(A) | C12X600112,5KVAB4M | CABOS | PODAS | 112,5KVA | (DCIM) | PRE1 | 112,5KVA | (DCIM) | 175ET005296879 | CE1 | AVENIDA</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="n">
+          <t>13200 | BF-A | 563620 | 15KV_1F1(A) | (DCIM) | 175ET005296879 | B1F | C12X600112,5KVAB4M | PRE1 | (DCIM)</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -1622,13 +1622,13 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | BCU | (DCIM) | P12 | ANCORAR | 3x336AN | CABOS | BT | ANCORAR | B1F | BT | (DCIM) | 3x336AN | 112,5KVA | CABOS | P11 | 112,5KVA | (DCIM) | AVENIDA | 13200 | AVENIDA | BF-A | 112,5KVA | 112,5KVA | 15KV_1F1(A) | 563620 | (DCIM) | P10 | CE1 | PRE4</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
+          <t>(DCIM) | 1RU6A | (DCIM) | ANCORAR | 3x336AN | CABOS | BT | ANCORAR | B1F | BT | (DCIM) | 3x336AN | 112,5KVA | CABOS | 112,5KVA | (DCIM) | AVENIDA | 13200 | AVENIDA | BF-A | 112,5KVA | 112,5KVA | 15KV_1F1(A) | 563620 | (DCIM) | CE1 | PRE4</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -1659,27 +1659,19 @@
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>B1F | (DCIM) | 2x1/0AN(4AN) | P13 | 112,5KVA | 30K | (DCIM) | 112,5KVA | 112,5KVA | 3x336AN(3/0AN) | 2x1/0AN(4AN) | Z | (DCIM) | 112,5KVA | 3x336AN | 112,5KVA | 112,5KVA | 3x185AX(5AZN) | 3x336AN | 112,5KVA | 30K | 112,5KVA | 30K | 400816F | 3X | 112,5KVA | P14 | 3X | 563618 | BT | (DCIM) | 112,5KVA | BT | 563618 | (DCIM) | 112,5KVA | AVENIDA | CAMPO | AVENIDA | (DCIM) | FERRAGEM | CF-H | 175ET005296879 | 112,5KVA | NUMERAÇÃO | BF-A | 175ET005296879 | CABOS | FERRAGEM | C12X600112,5KVAB1M</t>
+          <t>CABOS</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1712,13 +1704,13 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | P14 | BT | (DCIM) | BT | 3X | 30K | 3X | 30K | 112,5KVA | 3x336AN | 400816F | 112,5KVA | 112,5KVA | 112,5KVA | 3x336AN | (DCIM) | 3x185AX(5AZN) | 3x336AN(3/0AN) | 112,5KVA | 30K | 112,5KVA | 17064016 | 112,5KVA | Z | BF-A | 2x1/0AN(4AN) | 2x1/0AN(4AN) | 112,5KVA | 112,5KVA | B1F | 112,5KVA | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
+          <t>(DCIM) | (DCIM) | BT | BT | 3X | 3X | 1 | 3 | 8 | 3 | 5 | 6 | 112,5KVA | 112,5KVA | 3x336AN | 3x185AX(5AZN) | (DCIM) | 5 | 3x336AN(3/0AN) | 112,5KVA | 0 | Z | 112,5KVA | 2x1/0AN(4AN) | 2x1/0AN(4AN) | 2 | 5 | (DCIM) | B1F | (DCIM) | 17064016</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>

--- a/output_excel/17064027.xlsx
+++ b/output_excel/17064027.xlsx
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -563,30 +581,33 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>BM | GUINLE | 7275 | AVENIDA | CE1 | BF-A | PRE1 | 201734 | 15KV_1L(C) | CABOS | C10X300112,5KVAB1M112,5KVASMTG | 175ET005296879 | 15KV_1F1(A)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>25KVA C10X600112,5KVAB1M112,5KVAET1A112,5KVASMFL112,5KVAS45(1) CARGA 15KV_1F1(A) 15KV_1L(C) | C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL FORA CLANDESTINOS: PRUMO | C10X300112,5KVAB1M112,5KVASMTG | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | P2 | C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | C12X1000112,5KVAB4F112,5KVAS44(1) | GUINLE</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -614,22 +635,33 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>BM | GUINLE | AVENIDA</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>NAO</t>
+          <t>25KVA C10X600112,5KVAB1M112,5KVAET1A112,5KVASMFL112,5KVAS45(1) CARGA 15KV_1F1(A) 15KV_1L(C) | C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL FORA CLANDESTINOS: PRUMO | C10X300112,5KVAB1M112,5KVASMTG | P2 | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | GUINLE | C12X1000112,5KVAB4F112,5KVAS44(1)</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -653,30 +685,33 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>CABOS | C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | PRE1 | CE2</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | C12X1000112,5KVAB4F112,5KVAS44(1) | C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL FORA CLANDESTINOS: PRUMO | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | 25KVA C10X600112,5KVAB1M112,5KVAET1A112,5KVASMFL112,5KVAS45(1) CARGA 15KV_1F1(A) 15KV_1L(C) | P31 2 CS's | C10X300112,5KVAB1M112,5KVASMTG | P4-30</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -704,20 +739,31 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>GUIA | AVENIDA | 4957 | FERRAGEM | AVENIDA | EP | PERTO | PRUMO | EXPOSTA | CLANDESTINOS: | Q/R</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL FORA CLANDESTINOS: PRUMO | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | C10X300112,5KVAB1M112,5KVASMTG | C12X1000112,5KVAB4F112,5KVAS44(1) | C12X600112,5KVAB2M | 25KVA C10X600112,5KVAB1M112,5KVAET1A112,5KVASMFL112,5KVAS45(1) CARGA 15KV_1F1(A) 15KV_1L(C)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -743,30 +789,33 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>C12X600112,5KVAB2M | PRE1 | CE2 | CE2 | PRE1 | C12X600112,5KVAB2M | Q/R | ESTR.</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVAB2M | C12X600112,5KVAB2M | C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL FORA CLANDESTINOS: PRUMO | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | C12X1000112,5KVAB4F112,5KVAS44(1) | C12X600112,5KVAB4M PRE4 | CE2 PRE1 | CE2 PRE1</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -792,30 +841,33 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>PRE4 | C12X1000112,5KVAB4F112,5KVAS44(1) | CE4 | PODA</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>C12X1000112,5KVAB4F112,5KVAS44(1) | C10X300112,5KVAB2F112,5KVAC10x300,B2F,EPBFSA,SMTG112,5KVASMTG | CE4 PRE4 | PODA | C12X600112,5KVAB2M | P6 | CONEX. 27.63m P5 | CE2 PRE1</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -841,30 +893,33 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>CE2 | PRE1 | C12X600112,5KVAB2M | CE4 | PRE4 | C12X600112,5KVAB2M | C12X600112,5KVAB4M | PRE1 | PODA | EP | CE2 | PODAS | ESTR.</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVAB2M | C12X1000112,5KVAB4F112,5KVAS44(1) | C12X600112,5KVAB4M PRE4 | C12X600112,5KVAB2M | xP8 | P9 | P7x | CE2 PRE1</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -889,27 +944,30 @@
           <t>V1-2</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35.5m</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35.5M | 3x185AX(5AZN) | COMPARTILHANTES | 1x3x240(120)AX | LEGENDA | 3 | 1 | MT | COMPARTILHANTES</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
+          <t>35.5m</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>35.5M | MT 3x336AN(3/0AN) | MT 1x3x240(120)AX 3x336AN(3/0AN) | CMB 0099 | 34.5M | 12.3M | MT 3x336AN(3/0AN) | MT 1x3x240(120)AX 3x336AN(3/0AN)</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -934,27 +992,30 @@
           <t>V5-6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12.3m</t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12.3M | 3x336AN(3/0AN) | 17.3M | 2 | 1x3x240(120)AX | 1 | MT | 3x185AX(5AZN) | MT | VÃOS | 1x3x240(120)AX</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
+          <t>12.3m</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12.3M | 17.3M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 16.3M | 35.5M</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -979,27 +1040,30 @@
           <t>V9-10</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27.8m</t>
-        </is>
-      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2 | 27.8M | 3x185AX(5AZN) | C10X300112,5KVAB4M112,5KVAPRE4112,5KVASMFL112,5KVAS45(1) | 1x3x240(120)AX | 3x336AN(3/0AN) | MT | C12X300112,5KVAB4F112,5KVACE2112,5KVAS45(1)112,5KVASMFL | FORA</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
+          <t>27.8m</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27.8M | MT 3x336AN(3/0AN) | 18.8M | 12.3M | MT 3x336AN(3/0AN) | 17.3M | 2 V9-10 | MT 3x336AN(3/0AN)</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1025,30 +1089,33 @@
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>EP | 15681 | PODAS | 2 | CE4 | PRE4 | C12X600112,5KVAB4M</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVAB4M PRE4 | C12X1000112,5KVAB4F112,5KVAS44(1) | C12X600112,5KVAB2M | P9 | C12X600112,5KVAB2M | EP 15681 15681 | xP8 | C12X600112,5KVAB4M</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1073,27 +1140,30 @@
           <t>V6-7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16.3m</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3x336AN(3/0AN) | 16.3M | 2 | 17.3M | MT | 1x3x240(120)AX | 3x185AX(5AZN) | 3x185AX(5AZN) | 2 | 1x3x240(120)AX</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
+          <t>16.3m</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16.3M | 17.3M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 17.2M | MT 3x336AN(3/0AN)</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1118,29 +1188,32 @@
           <t>V10-11</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18.8m</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18.8M | 27.8M</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+          <t>18.8m</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>18.8M | 27.8M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 13.2M | MT 3x336AN(3/0AN) | 17.3M | 12.3M</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>NAO</t>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -1163,27 +1236,30 @@
           <t>V2-3</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>34.5m</t>
-        </is>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34.5M | 3x185AX(5AZN) | 1x3x240(120)AX | MT | 3 | 2 | MT | 3x336AN(3/0AN)</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n">
+          <t>34.5m</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>34.5M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 35.5M | MT 1x3x240(120)AX 3x336AN(3/0AN) | MT 1x3x240(120)AX 3x336AN(3/0AN) | 3M | 17.3M</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1211,20 +1287,31 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>EP | 15681 | PODAS | 2 | CABOS | CE4 | PRE4</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVAB4M PRE4 | C12X1000112,5KVAB4F112,5KVAS44(1) | C12X600112,5KVAB2M | P9 | EP 15681 15681 | C12X600112,5KVAB2M | C12X600112,5KVAB4M | xP8</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1249,27 +1336,30 @@
           <t>V7-8</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16.3m</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16.3M | 3x185AX(5AZN) | 1x3x240(120)AX | 1 | MT | 2 | 17.3M | MT</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="n">
+          <t>16.3m</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>16.3M | 17.3M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 17.2M | 13.2M</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1294,27 +1384,30 @@
           <t>V11-12</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13.2m</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13.2M | 3x336AN(3/0AN) | 1 | 1x3x240(120)AX | 3x185AX(5AZN) | MT | 34.9M</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="n">
+          <t>13.2m</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>13.2M | MT 3x336AN(3/0AN) | 34.9M | MT 3x336AN(3/0AN) | 18.8M | MT 3x336AN(3/0AN) | 16.3M | MT 3x336AN(3/0AN)</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1339,27 +1432,30 @@
           <t>V3-4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3m</t>
-        </is>
-      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3M | 3x185AX(5AZN) | 1X2X4AC | 3x336AN(3/0AN) | 1x3x240(120)AX | 3x336AN(3/0AN) | BT | 1X2X4AC | MT | MT | BT | 1x3x240(120)AX</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n">
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3M | MT 1x3x240(120)AX 3x336AN(3/0AN) | MT 1x3x240(120)AX 3x336AN(3/0AN) | 34.5M | 13.7M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 1x3x240(120)AX 3x336AN(3/0AN)</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1385,30 +1481,33 @@
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>PODAS | 2 | (DCIM) | B1F | EP | BT | CABOS | 3x336AN | PRE1 | C12X600112,5KVAB4M | CE1 | C12X600112,5KVAB4M | 15681 | ANCORAR | (DCIM) | PRE4 | 13200 | 1RU6A | 563620 | BF-A | (DCIM) | CE4</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVAB4M | C12X600112,5KVAB4M PRE4 | P10 | C12X600112,5KVAB2M | 2 PODAS | P11 | C10x600,B1M,M3F C12X600112,5KVAB1F112,5KVAET4A 112112,5KVA112,5KVA (DCIM) 15KV_1F1(A) | C12X600112,5KVAB1M</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1433,27 +1532,30 @@
           <t>V8-9</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>17.2m</t>
-        </is>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2 | 17.2M | 3x336AN(3/0AN) | 3x185AX(5AZN) | 1x3x240(120)AX | MT | 3x336AN(3/0AN) | 1x3x240(120)AX | MT | 16.3M | 3x185AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="n">
+          <t>17.2m</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>17.2M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 16.3M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 3M</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1478,27 +1580,30 @@
           <t>V12-13</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>34.9m</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34.9M | PRE1 | CE1 | C10x600,B1M,M3F | C12X600112,5KVAB1F112,5KVAET4A | 3x336AN(3/0AN) | 3 | 112112,5KVA112,5KVA | 1x3x240(120)AX | 3x185AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="n">
+          <t>34.9m</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>34.9M | MT 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 13.2M | 17.2M | NUMERAÇÃO FERRAGEM CF-H 563618 | MT 3x336AN(3/0AN) | 18.8M</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1523,27 +1628,30 @@
           <t>V4-5</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>13.7m</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13.7M | 1X2X4AC | 3M | 1 | 3x185AX(5AZN) | 3x336AN(3/0AN) | 1x3x240(120)AX | MT</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="n">
+          <t>13.7m</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>13.7M | 3M | MT 3x336AN(3/0AN) | MT 1x3x240(120)AX 3x336AN(3/0AN) | MT 1x3x240(120)AX 3x336AN(3/0AN) | MT 3x336AN(3/0AN) | 17.2M | MT 1x3x240(120)AX 3x336AN(3/0AN)</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1569,30 +1677,33 @@
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>13200 | BF-A | 563620 | 15KV_1F1(A) | (DCIM) | 175ET005296879 | B1F | C12X600112,5KVAB4M | PRE1 | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVAB4M | C10x600,B1M,M3F C12X600112,5KVAB1F112,5KVAET4A 112112,5KVA112,5KVA (DCIM) 15KV_1F1(A) | C12X600112,5KVAB1M | C12X600112,5KVAB4M PRE4 | 2 V1-3 13200 | 563620 | P11 | CE1 PRE1</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1620,20 +1731,31 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | 1RU6A | (DCIM) | ANCORAR | 3x336AN | CABOS | BT | ANCORAR | B1F | BT | (DCIM) | 3x336AN | 112,5KVA | CABOS | 112,5KVA | (DCIM) | AVENIDA | 13200 | AVENIDA | BF-A | 112,5KVA | 112,5KVA | 15KV_1F1(A) | 563620 | (DCIM) | CE1 | PRE4</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVAB1M | (DCIM) 1RU6A (DCIM) | C12X600112,5KVAB4M | C10x600,B1M,M3F C12X600112,5KVAB1F112,5KVAET4A 112112,5KVA112,5KVA (DCIM) 15KV_1F1(A) | 2 CS's 112,5KVA 1x4ANA | P11</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1661,20 +1783,31 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>CABOS</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2 CS's | C12X600112,5KVAB1M112,5KVACE2 | EP 15681 561895 | SOLICITANTE | ETAPA 5 2 V1-3 17064016 | ENDERECO | (DCIM) BT BT 3X | C12x600,B1F,CF-H 17204</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1702,20 +1835,31 @@
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | (DCIM) | BT | BT | 3X | 3X | 1 | 3 | 8 | 3 | 5 | 6 | 112,5KVA | 112,5KVA | 3x336AN | 3x185AX(5AZN) | (DCIM) | 5 | 3x336AN(3/0AN) | 112,5KVA | 0 | Z | 112,5KVA | 2x1/0AN(4AN) | 2x1/0AN(4AN) | 2 | 5 | (DCIM) | B1F | (DCIM) | 17064016</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>(DCIM) BT BT 3X | P14 3X 3 3 6 1 8 5 | C12X600112,5KVAB1M112,5KVACE2 | 112,5KVA 1x4ANA (DCIM) 112,5KVA 3x185AX(5AZN) 5 | 3x336AN(3/0AN) 0 112,5KVA 112,5KVA CRUZ 2x1/0AN(4AN) | C12X600112,5KVAB1M | C12X600112,5KVAB1F112,5KVACF-H PRE3 | P13</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
